--- a/Phenotype/Tables/EPS_TableS9B_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS9B_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,22 +367,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Df</t>
+          <t>NumDF</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>DenDF</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Sum Sq</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>F value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pr(&gt;F)</t>
         </is>
       </c>
     </row>
@@ -402,17 +407,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.841</t>
+          <t>1.114</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2.381</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.126</t>
         </is>
       </c>
     </row>
@@ -432,17 +442,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>0.911</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>1.947</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.166</t>
         </is>
       </c>
     </row>
@@ -462,15 +477,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.850</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>1.817</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.180</t>
         </is>
@@ -484,20 +504,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Residuals</t>
+          <t>Rep</t>
         </is>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>39.541</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>20.497</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6.258</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>&lt; 0.001</t>
         </is>
       </c>
     </row>
@@ -517,17 +547,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.051</t>
+          <t>1.955</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>6.138</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.015</t>
         </is>
       </c>
     </row>
@@ -547,17 +582,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.683</t>
+          <t>0.943</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2.960</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.088</t>
         </is>
       </c>
     </row>
@@ -577,15 +617,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>8.494</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>26.665</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -599,20 +644,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Residuals</t>
+          <t>Rep</t>
         </is>
       </c>
       <c r="C9">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32.215</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9.938</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6.240</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>&lt; 0.001</t>
         </is>
       </c>
     </row>
@@ -632,17 +687,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>2.112</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.147</t>
         </is>
       </c>
     </row>
@@ -662,15 +722,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18.334</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>235.398</t>
+          <t>111.389</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>167.352</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -692,15 +757,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.926</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.568</t>
+          <t>17.556</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
+        <is>
+          <t>26.376</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -714,20 +784,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Residuals</t>
+          <t>Rep</t>
         </is>
       </c>
       <c r="C13">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.801</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3.736</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.123</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.347</t>
         </is>
       </c>
     </row>

--- a/Phenotype/Tables/EPS_TableS9B_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS9B_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,25 +367,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NumDF</t>
+          <t>Sum Sq</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DenDF</t>
+          <t>Df</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sum Sq</t>
+          <t>F value</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>F value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pr(&gt;F)</t>
         </is>
@@ -402,25 +397,20 @@
           <t>Morphology</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>2.381</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>2.381</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>0.126</t>
         </is>
@@ -437,25 +427,20 @@
           <t>PC1</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.681</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>1.947</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>1.947</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>0.166</t>
         </is>
@@ -472,25 +457,20 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.636</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.850</t>
+          <t>1.817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>1.817</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>0.180</t>
         </is>
@@ -504,30 +484,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rep</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>812.0</t>
-        </is>
+          <t>Residuals</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>39.541</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>113</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.497</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6.258</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>&lt; 0.001</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -542,25 +512,20 @@
           <t>Morphology</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.955</t>
+          <t>6.138</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>6.138</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
@@ -577,25 +542,20 @@
           <t>PC1</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>2.960</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>0.088</t>
         </is>
@@ -612,25 +572,20 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7.602</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8.494</t>
+          <t>26.665</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>26.665</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -644,30 +599,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rep</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>580.0</t>
-        </is>
+          <t>Residuals</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>32.215</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>113</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9.938</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>6.240</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>&lt; 0.001</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -682,27 +627,22 @@
           <t>Morphology</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.234</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>3.008</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.112</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.147</t>
+          <t>0.086</t>
         </is>
       </c>
     </row>
@@ -717,25 +657,20 @@
           <t>PC1</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>18.565</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>111.389</t>
+          <t>238.363</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>167.352</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -752,25 +687,20 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.926</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17.556</t>
+          <t>37.568</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>26.376</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -784,30 +714,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rep</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>693.0</t>
-        </is>
+          <t>Residuals</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8.801</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>113</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.736</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.123</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.347</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
